--- a/AAII_Financials/Yearly/LRLCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LRLCY_YR_FIN.xlsx
@@ -2620,13 +2620,13 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7194100</v>
+        <v>28523800</v>
       </c>
       <c r="E72" s="3">
-        <v>6635000</v>
+        <v>23349700</v>
       </c>
       <c r="F72" s="3">
-        <v>6835400</v>
+        <v>22088100</v>
       </c>
       <c r="G72" s="3">
         <v>18576700</v>
